--- a/test 2.xlsx
+++ b/test 2.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,8 +47,11 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +66,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEFEFEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6E6E6"/>
+        <bgColor rgb="00E6E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0092D050"/>
+        <bgColor rgb="0092D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004F81BD"/>
+        <bgColor rgb="004F81BD"/>
       </patternFill>
     </fill>
   </fills>
@@ -100,9 +133,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -145,22 +178,26 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -169,6 +206,65 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -535,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -546,13 +642,13 @@
     <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="25" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>NOMBRE DE LA EMPRESA</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>LOGO DE LA EMPRESA</t>
         </is>
@@ -641,22 +737,22 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>MOTOR ELEC 50HP 3600 RPM BOMBA</t>
+          <t>MANEJO DE AGUAS RESIDUALES</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D9" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="11" t="n">
-        <v>6770060</v>
+        <v>8949</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>6770060</v>
+        <v>8949</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -667,22 +763,22 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>MOTOR ELEC 60HP 3600 RPM BOMBA</t>
+          <t>DESCAPOTE MAQUINA</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>7835605</v>
+        <v>3264</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>7835605</v>
+        <v>3264</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -693,22 +789,22 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>MOTOR ELEC 100HP 3600 RPM BOMBA</t>
+          <t>TUB CONCRETO SIMPLED=15"UNION CAUCHO</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D11" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>11167041</v>
+        <v>91943</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>11167041</v>
+        <v>91943</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -719,22 +815,22 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>MOTOR ELEC 150HP 3600 RPM BOMBA</t>
+          <t>TUBERIA CONCRETO HR C II D=1.0 M</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D12" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>17441501</v>
+        <v>451541</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>17441501</v>
+        <v>451541</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -748,7 +844,7 @@
       <c r="D13" s="13" t="n"/>
       <c r="E13" s="13" t="n"/>
       <c r="F13" s="14" t="n">
-        <v>43214207</v>
+        <v>555697</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -766,7 +862,7 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>MOTOR ELEC 30HP 3600 RPM BOMBA</t>
+          <t>CAMARA INSPECCION TIPO I H=1.51-2.00 MTS</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -778,10 +874,10 @@
         <v>1</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>3943064</v>
+        <v>849322</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>3943064</v>
+        <v>849322</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -792,7 +888,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>BOMBA SUMERG3.0 HP LAPICERO 4" A.INOX</t>
+          <t>VALVULA CHAPALETA Q=4.10L/SEG S=1.5M 10"</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -804,10 +900,10 @@
         <v>1</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>4802037</v>
+        <v>2240072</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>4802037</v>
+        <v>2240072</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -818,80 +914,80 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>BOMBA SUMERG 15 HP LAPICERO 6" A.INOX</t>
+          <t>TUB PVC NOVAFORT 12"</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>UND</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D18" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>11351511</v>
+        <v>142682</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>11351511</v>
+        <v>142682</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>BOMBA SUMERG 20HP LAPICERO 6" A.INOX</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>SUBTOTAL 2. 2:</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="14" t="n">
+        <v>3232076</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. 3 </t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>MOTOR ELEC 25HP 3600 RPM BOMBA</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>UND</t>
         </is>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D22" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="11" t="n">
-        <v>13791162</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>13791162</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>SUBTOTAL 2. 2:</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="14" t="n">
-        <v>33887774</v>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. 3 </t>
-        </is>
+      <c r="E22" s="11" t="n">
+        <v>2884414</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>2884414</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>BOMBA SUMERG 25HP LAPICERO 6" A.INOX</t>
+          <t>BOMBA SUMERG1.0 HP LAPICERO 4" BRONCE</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -903,21 +999,21 @@
         <v>1</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>16426248</v>
+        <v>2758377</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>16426248</v>
+        <v>2758377</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>BOMBA SUMERG 30HP LAPICERO 6" A.INOX</t>
+          <t>REJILLA HIERRO D=1/2" E=1/2 1.50x.40MTS</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -929,238 +1025,213 @@
         <v>1</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>23701720</v>
+        <v>145391</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>23701720</v>
+        <v>145391</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>3.3</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>BOMBA SUMERG 40HP LAPICERO 6" A.INOX</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>26255148</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>26255148</v>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>3.4</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>BOMBA SUMERG 50HP LAPICERO 6" A.INOX</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>UND</t>
-        </is>
-      </c>
-      <c r="D26" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>30578425</v>
-      </c>
-      <c r="F26" s="11" t="n">
-        <v>30578425</v>
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>SUBTOTAL 3. 3:</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="14" t="n">
+        <v>5788182</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>SUBTOTAL 3. 3:</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="14" t="n">
-        <v>96961541</v>
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>VALOR COSTOS DIRECTOS</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="16" t="n">
+        <v>9575955</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="19" t="n"/>
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>VALOR COSTOS DIRECTOS</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="16" t="n">
-        <v>174063522</v>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="21" t="n">
+        <v>9575955</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>COSTOS INDIRECTOS</t>
-        </is>
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="E31" s="23" t="inlineStr">
+        <is>
+          <t>514.34%</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="n">
+        <v>49252650.2548176</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="D32" s="18" t="inlineStr">
-        <is>
-          <t>VALOR COSTOS DIRECTOS</t>
-        </is>
-      </c>
-      <c r="F32" s="19" t="n">
-        <v>174063522</v>
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>IMPREVISTOS</t>
+        </is>
+      </c>
+      <c r="E32" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="n">
+        <v>478797.75</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>ADMINISTRACIÓN</t>
-        </is>
-      </c>
-      <c r="E33" s="20" t="inlineStr">
-        <is>
-          <t>54.87%</t>
-        </is>
-      </c>
-      <c r="F33" s="21" t="n">
-        <v>95504699.08277941</v>
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="22" t="inlineStr">
+        <is>
+          <t>UTILIDAD</t>
+        </is>
+      </c>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="n">
+        <v>478797.75</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="D34" s="18" t="inlineStr">
-        <is>
-          <t>IMPREVISTOS</t>
-        </is>
-      </c>
-      <c r="E34" s="20" t="inlineStr">
-        <is>
-          <t>5.00%</t>
+      <c r="A34" s="19" t="n"/>
+      <c r="B34" s="19" t="n"/>
+      <c r="C34" s="19" t="n"/>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>TOTAL AIU</t>
+        </is>
+      </c>
+      <c r="E34" s="25" t="inlineStr">
+        <is>
+          <t>524.34%</t>
         </is>
       </c>
       <c r="F34" s="21" t="n">
-        <v>8703176.1</v>
+        <v>50210245.7548176</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>UTILIDAD</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="inlineStr">
-        <is>
-          <t>5.00%</t>
-        </is>
-      </c>
-      <c r="F35" s="21" t="n">
-        <v>8703176.1</v>
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>IVA SOBRE LA UTILIDAD</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>0.15%</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="n">
+        <v>90971.57249999999</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL AIU</t>
-        </is>
-      </c>
-      <c r="E36" s="20" t="inlineStr">
-        <is>
-          <t>64.87%</t>
-        </is>
-      </c>
-      <c r="F36" s="19" t="n">
-        <v>112911051.2827794</v>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>IVA SOBRE LA UTILIDAD</t>
-        </is>
-      </c>
-      <c r="E37" s="20" t="inlineStr">
-        <is>
-          <t>0.58%</t>
-        </is>
-      </c>
-      <c r="F37" s="21" t="n">
-        <v>1653603.459</v>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="D38" s="22" t="inlineStr">
+      <c r="A36" s="19" t="n"/>
+      <c r="B36" s="19" t="n"/>
+      <c r="C36" s="19" t="n"/>
+      <c r="D36" s="20" t="inlineStr">
         <is>
           <t>VALOR TOTAL PRESUPUESTO</t>
         </is>
       </c>
-      <c r="E38" s="23" t="n"/>
-      <c r="F38" s="16" t="n">
-        <v>288628176.7417794</v>
-      </c>
-    </row>
-    <row r="40" ht="25" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
-        <is>
-          <t>VALOR TOTAL PRESUPUESTO: DOSCIENTOS OCHENTA Y OCHO MILLONES SEISCIENTOS VEINTIOCHO MIL CIENTO SETENTA Y SEIS PESOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" s="25" t="inlineStr">
+      <c r="E36" s="19" t="n"/>
+      <c r="F36" s="21" t="n">
+        <v>59877172.3273176</v>
+      </c>
+    </row>
+    <row r="38" ht="25" customHeight="1">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>VALOR TOTAL PRESUPUESTO: CINCUENTA Y NUEVE MILLONES OCHOCIENTOS SETENTA Y SIETE MIL CIENTO SETENTA Y DOS PESOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" s="27" t="inlineStr">
         <is>
           <t>PLAZO DE ENTREGA: (DÍAS CALENDARIO)</t>
         </is>
       </c>
-      <c r="E43" s="25" t="n">
+      <c r="E41" s="27" t="n">
         <v>90</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="26" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="28" t="inlineStr">
         <is>
           <t>FIRMA DEL REPRESENTANTE LEGAL</t>
         </is>
       </c>
     </row>
+    <row r="45"/>
+    <row r="46"/>
     <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="C41:D41"/>
     <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A19:E19"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A46:C49"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A44:C47"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="D1:F1"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
@@ -1174,9 +1245,889 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NOMBRE DE LA EMPRESA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LOGO DE LA EMPRESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>DISCRIMINACIÓN DEL AIU</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Obra:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>ESCRIBA AQUÍ EL NOMBRE DE LA OBRA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FECHA:</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>19-sept-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>QUIEN ELABORÓ:</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="30" t="inlineStr">
+        <is>
+          <t>COSTOS ADMINISTRATIVOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr"/>
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>VALOR MENSUAL</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>%DEDIC</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>MESES</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>VALOR PARCIAL</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>% SOBRE CD</t>
+        </is>
+      </c>
+      <c r="G8" s="31" t="inlineStr">
+        <is>
+          <t>VALOR EN PESOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>PERSONAL TÉCNICO Y ADM. (Incl. Prest. Soc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>DIRECTOR DE OBRA ING CIVIL</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="n">
+        <v>3348124.71</v>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="D10" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>10044374.13</v>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>104.89%</t>
+        </is>
+      </c>
+      <c r="G10" s="34" t="n">
+        <v>10044374.13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>RESIDENTE DE OBRA ING CIVIL</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="n">
+        <v>2521178.24</v>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="34" t="n">
+        <v>15127069.44</v>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>157.97%</t>
+        </is>
+      </c>
+      <c r="G11" s="34" t="n">
+        <v>15127069.44</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>TECNICO O TECNOLOGO MAESTRO DE OBRA</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="n">
+        <v>1815248.34</v>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="D12" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>10891490.04</v>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>113.74%</t>
+        </is>
+      </c>
+      <c r="G12" s="34" t="n">
+        <v>10891490.04</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>COORDINADOR DE SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="n">
+        <v>1815248.34</v>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="D13" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="34" t="n">
+        <v>10891490.04</v>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>113.74%</t>
+        </is>
+      </c>
+      <c r="G13" s="34" t="n">
+        <v>10891490.04</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="inlineStr">
+        <is>
+          <t>TOTAL COSTOS ADMINISTRATIVOS (SUMA):</t>
+        </is>
+      </c>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="37" t="n">
+        <v>46954423.65</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="38" t="inlineStr">
+        <is>
+          <t>OFICINA, PAPELERÍA Y OTROS:</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr"/>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>VALOR MENSUAL</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>%DEDIC</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>MESES</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
+        <is>
+          <t>VALOR PARCIAL</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>% SOBRE CD</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="inlineStr">
+        <is>
+          <t>VALOR EN PESOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>Costo oficina</t>
+        </is>
+      </c>
+      <c r="B19" s="34" t="n">
+        <v>300000</v>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>19.2768%</t>
+        </is>
+      </c>
+      <c r="D19" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" s="34" t="n">
+        <v>346982.4</v>
+      </c>
+      <c r="F19" s="33" t="inlineStr">
+        <is>
+          <t>3.62%</t>
+        </is>
+      </c>
+      <c r="G19" s="34" t="n">
+        <v>346982.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>Papelería / Fotocopias / Otros</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>19.2768%</t>
+        </is>
+      </c>
+      <c r="D20" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" s="34" t="n">
+        <v>115660.8</v>
+      </c>
+      <c r="F20" s="33" t="inlineStr">
+        <is>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="G20" s="34" t="n">
+        <v>115660.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t>LEGALIZACIÓN DEL CONTRATO (Pólizas):</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr"/>
+      <c r="B24" s="31" t="inlineStr">
+        <is>
+          <t>%Requerido</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="inlineStr">
+        <is>
+          <t>Duración</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>%Prima</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>Vr. TI Contrato</t>
+        </is>
+      </c>
+      <c r="F24" s="31" t="inlineStr">
+        <is>
+          <t>%Dedic Directos</t>
+        </is>
+      </c>
+      <c r="G24" s="31" t="inlineStr">
+        <is>
+          <t>Valor en Pesos</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>Póliza de Cumplimiento</t>
+        </is>
+      </c>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="C25" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" s="33" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="E25" s="34" t="n">
+        <v>7979.96</v>
+      </c>
+      <c r="F25" s="33" t="inlineStr">
+        <is>
+          <t>19.28%</t>
+        </is>
+      </c>
+      <c r="G25" s="34" t="n">
+        <v>1538.28</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>Póliza de Anticipo</t>
+        </is>
+      </c>
+      <c r="B26" s="33" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="C26" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D26" s="33" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="E26" s="34" t="n">
+        <v>39899.81</v>
+      </c>
+      <c r="F26" s="33" t="inlineStr">
+        <is>
+          <t>19.28%</t>
+        </is>
+      </c>
+      <c r="G26" s="34" t="n">
+        <v>7691.41</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>Póliza RC Extracontractual</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" s="33" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="E27" s="34" t="n">
+        <v>11969.94</v>
+      </c>
+      <c r="F27" s="33" t="inlineStr">
+        <is>
+          <t>19.28%</t>
+        </is>
+      </c>
+      <c r="G27" s="34" t="n">
+        <v>2307.42</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="33" t="inlineStr">
+        <is>
+          <t>Póliza de Estabilidad</t>
+        </is>
+      </c>
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="C28" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" s="33" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="E28" s="34" t="n">
+        <v>3989.98</v>
+      </c>
+      <c r="F28" s="33" t="inlineStr">
+        <is>
+          <t>19.28%</t>
+        </is>
+      </c>
+      <c r="G28" s="34" t="n">
+        <v>769.14</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="33" t="inlineStr">
+        <is>
+          <t>Calidad del Servicio</t>
+        </is>
+      </c>
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" s="33" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="E29" s="34" t="n">
+        <v>7979.96</v>
+      </c>
+      <c r="F29" s="33" t="inlineStr">
+        <is>
+          <t>19.28%</t>
+        </is>
+      </c>
+      <c r="G29" s="34" t="n">
+        <v>1538.28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
+          <t>Calidad y Correcto Funcionamiento</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" s="33" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="E30" s="34" t="n">
+        <v>7979.96</v>
+      </c>
+      <c r="F30" s="33" t="inlineStr">
+        <is>
+          <t>19.28%</t>
+        </is>
+      </c>
+      <c r="G30" s="34" t="n">
+        <v>1538.28</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>Póliza Salarios y P.S.</t>
+        </is>
+      </c>
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="C31" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" s="33" t="inlineStr">
+        <is>
+          <t>1.00%</t>
+        </is>
+      </c>
+      <c r="E31" s="34" t="n">
+        <v>3989.98</v>
+      </c>
+      <c r="F31" s="33" t="inlineStr">
+        <is>
+          <t>19.28%</t>
+        </is>
+      </c>
+      <c r="G31" s="34" t="n">
+        <v>769.14</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="38" t="inlineStr">
+        <is>
+          <t>DESCUENTOS SOBRE EL CONTRATO:</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="31" t="inlineStr"/>
+      <c r="B35" s="31" t="inlineStr">
+        <is>
+          <t>Vr. TI Contrato</t>
+        </is>
+      </c>
+      <c r="C35" s="31" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D35" s="31" t="inlineStr">
+        <is>
+          <t>Valor en Pesos</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t>Estampilla pro Desarrollo</t>
+        </is>
+      </c>
+      <c r="B36" s="34" t="n">
+        <v>9575955</v>
+      </c>
+      <c r="C36" s="33" t="inlineStr">
+        <is>
+          <t>4.0%</t>
+        </is>
+      </c>
+      <c r="D36" s="34" t="n">
+        <v>383038.2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="32" t="inlineStr">
+        <is>
+          <t>Estampilla pro Univalle</t>
+        </is>
+      </c>
+      <c r="B37" s="34" t="n">
+        <v>9575955</v>
+      </c>
+      <c r="C37" s="33" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+      <c r="D37" s="34" t="n">
+        <v>95759.55</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="32" t="inlineStr">
+        <is>
+          <t>Estampilla pro Hospital</t>
+        </is>
+      </c>
+      <c r="B38" s="34" t="n">
+        <v>9575955</v>
+      </c>
+      <c r="C38" s="33" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+      <c r="D38" s="34" t="n">
+        <v>95759.55</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="32" t="inlineStr">
+        <is>
+          <t>Estampilla pro Cultura</t>
+        </is>
+      </c>
+      <c r="B39" s="34" t="n">
+        <v>9575955</v>
+      </c>
+      <c r="C39" s="33" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+      <c r="D39" s="34" t="n">
+        <v>95759.55</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t>Estampilla pro Pacífico</t>
+        </is>
+      </c>
+      <c r="B40" s="34" t="n">
+        <v>9575955</v>
+      </c>
+      <c r="C40" s="33" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+      <c r="D40" s="34" t="n">
+        <v>95759.55</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t>Estampilla pro Deporte</t>
+        </is>
+      </c>
+      <c r="B41" s="34" t="n">
+        <v>9575955</v>
+      </c>
+      <c r="C41" s="33" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="D41" s="34" t="n">
+        <v>191519.1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="32" t="inlineStr">
+        <is>
+          <t>Estampilla pro Adulto Mayor</t>
+        </is>
+      </c>
+      <c r="B42" s="34" t="n">
+        <v>9575955</v>
+      </c>
+      <c r="C42" s="33" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="D42" s="34" t="n">
+        <v>191519.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="32" t="inlineStr">
+        <is>
+          <t>Estampilla Familiar</t>
+        </is>
+      </c>
+      <c r="B43" s="34" t="n">
+        <v>9575955</v>
+      </c>
+      <c r="C43" s="33" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="D43" s="34" t="n">
+        <v>191519.1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t>Contribución Especial</t>
+        </is>
+      </c>
+      <c r="B44" s="34" t="n">
+        <v>9575955</v>
+      </c>
+      <c r="C44" s="33" t="inlineStr">
+        <is>
+          <t>5.0%</t>
+        </is>
+      </c>
+      <c r="D44" s="34" t="n">
+        <v>478797.75</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="35" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN:</t>
+        </is>
+      </c>
+      <c r="B47" s="36" t="n"/>
+      <c r="C47" s="36" t="n"/>
+      <c r="D47" s="39" t="inlineStr">
+        <is>
+          <t>514.34%</t>
+        </is>
+      </c>
+      <c r="E47" s="37" t="n">
+        <v>49252650.2548176</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>IMPREVISTOS:</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="n">
+        <v>478797.75</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>UTILIDAD:</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="n">
+        <v>478797.75</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>IVA SOBRE LA UTILIDAD:</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="23" t="inlineStr">
+        <is>
+          <t>19.00%</t>
+        </is>
+      </c>
+      <c r="E50" s="24" t="n">
+        <v>90971.57249999999</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="35" t="inlineStr">
+        <is>
+          <t>COSTO TOTAL DEL AIU:</t>
+        </is>
+      </c>
+      <c r="B51" s="36" t="n"/>
+      <c r="C51" s="36" t="n"/>
+      <c r="D51" s="39" t="inlineStr">
+        <is>
+          <t>525.29%</t>
+        </is>
+      </c>
+      <c r="E51" s="37" t="n">
+        <v>50301217.3273176</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A23:G23"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1187,9 +2138,4200 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NOMBRE DE LA EMPRESA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LOGO DE LA EMPRESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>ANÁLISIS DE PRECIOS UNITARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Obra:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>ESCRIBA AQUÍ EL NOMBRE DE LA OBRA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FECHA:</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>19-sept-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>QUIEN ELABORÓ:</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>01-01-08 - MANEJO DE AGUAS RESIDUALES</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UNIDAD:</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ITEM:</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>01-01-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>CÓDIGO RECURSO</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>CANT.</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>DESP.%</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>PRECIO UNIT</t>
+        </is>
+      </c>
+      <c r="G9" s="31" t="inlineStr">
+        <is>
+          <t>VALOR PARCIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>--- MANO DE OBRA ---</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>MOAG01</t>
+        </is>
+      </c>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA ALBANILERIA1 AYUDANTE</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F11" s="34" t="n">
+        <v>8949</v>
+      </c>
+      <c r="G11" s="34" t="n">
+        <v>8949</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MANO DE OBRA:</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="42" t="n">
+        <v>8949</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>COSTO DIRECTO:</t>
+        </is>
+      </c>
+      <c r="B13" s="44" t="n"/>
+      <c r="C13" s="44" t="n"/>
+      <c r="D13" s="44" t="n"/>
+      <c r="E13" s="44" t="n"/>
+      <c r="F13" s="44" t="n"/>
+      <c r="G13" s="45" t="n">
+        <v>8949</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="46" t="inlineStr">
+        <is>
+          <t>COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="44" t="n"/>
+      <c r="E15" s="44" t="n"/>
+      <c r="F15" s="44" t="n"/>
+      <c r="G15" s="44" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>514.34%</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>46027.99064222448</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>IMPREVISTOS</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>447.45</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>447.45</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>IVA SOBRE LA UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>19.00%</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>1700.31</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>525.29%</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>47007.90614222448</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>VALOR TOTAL ITEM:</t>
+        </is>
+      </c>
+      <c r="B21" s="44" t="n"/>
+      <c r="C21" s="44" t="n"/>
+      <c r="D21" s="44" t="n"/>
+      <c r="E21" s="44" t="n"/>
+      <c r="F21" s="44" t="n"/>
+      <c r="G21" s="45" t="n">
+        <v>55956.90614222448</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="40" t="inlineStr">
+        <is>
+          <t>01-02-02 - DESCAPOTE MAQUINA</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>UNIDAD:</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ITEM:</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>01-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
+          <t>CÓDIGO RECURSO</t>
+        </is>
+      </c>
+      <c r="B27" s="31" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>CANT.</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>DESP.%</t>
+        </is>
+      </c>
+      <c r="F27" s="31" t="inlineStr">
+        <is>
+          <t>PRECIO UNIT</t>
+        </is>
+      </c>
+      <c r="G27" s="31" t="inlineStr">
+        <is>
+          <t>VALOR PARCIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>--- MANO DE OBRA ---</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>MOAG01</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA ALBANILERIA1 AYUDANTE</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D29" s="34" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E29" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F29" s="34" t="n">
+        <v>8949</v>
+      </c>
+      <c r="G29" s="34" t="n">
+        <v>357.96</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MANO DE OBRA:</t>
+        </is>
+      </c>
+      <c r="B30" s="36" t="n"/>
+      <c r="C30" s="36" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="36" t="n"/>
+      <c r="F30" s="36" t="n"/>
+      <c r="G30" s="42" t="n">
+        <v>357.96</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>--- EQUIPO ---</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>MQ0210</t>
+        </is>
+      </c>
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>RETROEXCAVADORA CARGADORA</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="D32" s="34" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="E32" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F32" s="34" t="n">
+        <v>101150</v>
+      </c>
+      <c r="G32" s="34" t="n">
+        <v>202.3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>MQ0301</t>
+        </is>
+      </c>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>HERRAMIENTA MENOR</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>GLB</t>
+        </is>
+      </c>
+      <c r="D33" s="34" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E33" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F33" s="34" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G33" s="34" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t>MQ0205</t>
+        </is>
+      </c>
+      <c r="B34" s="32" t="inlineStr">
+        <is>
+          <t>RETROEXCAVADORA JD-510</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="D34" s="34" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E34" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F34" s="34" t="n">
+        <v>88000</v>
+      </c>
+      <c r="G34" s="34" t="n">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL EQUIPO:</t>
+        </is>
+      </c>
+      <c r="B35" s="36" t="n"/>
+      <c r="C35" s="36" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="42" t="n">
+        <v>2906.3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="43" t="inlineStr">
+        <is>
+          <t>COSTO DIRECTO:</t>
+        </is>
+      </c>
+      <c r="B36" s="44" t="n"/>
+      <c r="C36" s="44" t="n"/>
+      <c r="D36" s="44" t="n"/>
+      <c r="E36" s="44" t="n"/>
+      <c r="F36" s="44" t="n"/>
+      <c r="G36" s="45" t="n">
+        <v>3264.26</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="46" t="inlineStr">
+        <is>
+          <t>COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B38" s="44" t="n"/>
+      <c r="C38" s="44" t="n"/>
+      <c r="D38" s="44" t="n"/>
+      <c r="E38" s="44" t="n"/>
+      <c r="F38" s="44" t="n"/>
+      <c r="G38" s="44" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="23" t="inlineStr">
+        <is>
+          <t>514.34%</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="n">
+        <v>16789.28692968909</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>IMPREVISTOS</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="n">
+        <v>163.213</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="n">
+        <v>163.213</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>IVA SOBRE LA UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="23" t="inlineStr">
+        <is>
+          <t>19.00%</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="n">
+        <v>620.2094000000001</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="23" t="inlineStr">
+        <is>
+          <t>525.29%</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="n">
+        <v>17146.72339968909</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="43" t="inlineStr">
+        <is>
+          <t>VALOR TOTAL ITEM:</t>
+        </is>
+      </c>
+      <c r="B44" s="44" t="n"/>
+      <c r="C44" s="44" t="n"/>
+      <c r="D44" s="44" t="n"/>
+      <c r="E44" s="44" t="n"/>
+      <c r="F44" s="44" t="n"/>
+      <c r="G44" s="45" t="n">
+        <v>20410.98339968909</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="40" t="inlineStr">
+        <is>
+          <t>02-03-07 - TUB CONCRETO SIMPLED=15"UNION CAUCHO</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>UNIDAD:</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ITEM:</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>02-03-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="31" t="inlineStr">
+        <is>
+          <t>CÓDIGO RECURSO</t>
+        </is>
+      </c>
+      <c r="B50" s="31" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN</t>
+        </is>
+      </c>
+      <c r="C50" s="31" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D50" s="31" t="inlineStr">
+        <is>
+          <t>CANT.</t>
+        </is>
+      </c>
+      <c r="E50" s="31" t="inlineStr">
+        <is>
+          <t>DESP.%</t>
+        </is>
+      </c>
+      <c r="F50" s="31" t="inlineStr">
+        <is>
+          <t>PRECIO UNIT</t>
+        </is>
+      </c>
+      <c r="G50" s="31" t="inlineStr">
+        <is>
+          <t>VALOR PARCIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="32" t="inlineStr">
+        <is>
+          <t>--- MANO DE OBRA ---</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="32" t="inlineStr">
+        <is>
+          <t>MOAG12</t>
+        </is>
+      </c>
+      <c r="B52" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA ALBANILERIA2 AYUDANTE-1 OFI</t>
+        </is>
+      </c>
+      <c r="C52" s="32" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D52" s="34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E52" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F52" s="34" t="n">
+        <v>32845</v>
+      </c>
+      <c r="G52" s="34" t="n">
+        <v>16422.5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="32" t="inlineStr">
+        <is>
+          <t>MOTO01</t>
+        </is>
+      </c>
+      <c r="B53" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA TOPOGRAFIA1 CADENERO-1 TOP</t>
+        </is>
+      </c>
+      <c r="C53" s="32" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D53" s="34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E53" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F53" s="34" t="n">
+        <v>66168</v>
+      </c>
+      <c r="G53" s="34" t="n">
+        <v>661.6800000000001</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MANO DE OBRA:</t>
+        </is>
+      </c>
+      <c r="B54" s="36" t="n"/>
+      <c r="C54" s="36" t="n"/>
+      <c r="D54" s="36" t="n"/>
+      <c r="E54" s="36" t="n"/>
+      <c r="F54" s="36" t="n"/>
+      <c r="G54" s="42" t="n">
+        <v>17084.18</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="32" t="inlineStr">
+        <is>
+          <t>--- EQUIPO ---</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+      <c r="F55" s="4" t="n"/>
+      <c r="G55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="32" t="inlineStr">
+        <is>
+          <t>MQ0301</t>
+        </is>
+      </c>
+      <c r="B56" s="32" t="inlineStr">
+        <is>
+          <t>HERRAMIENTA MENOR</t>
+        </is>
+      </c>
+      <c r="C56" s="32" t="inlineStr">
+        <is>
+          <t>GLB</t>
+        </is>
+      </c>
+      <c r="D56" s="34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E56" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F56" s="34" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G56" s="34" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL EQUIPO:</t>
+        </is>
+      </c>
+      <c r="B57" s="36" t="n"/>
+      <c r="C57" s="36" t="n"/>
+      <c r="D57" s="36" t="n"/>
+      <c r="E57" s="36" t="n"/>
+      <c r="F57" s="36" t="n"/>
+      <c r="G57" s="42" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="32" t="inlineStr">
+        <is>
+          <t>--- MATERIALES ---</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="32" t="inlineStr">
+        <is>
+          <t>001350</t>
+        </is>
+      </c>
+      <c r="B59" s="32" t="inlineStr">
+        <is>
+          <t>GRAVA TRITURADA.3/4</t>
+        </is>
+      </c>
+      <c r="C59" s="32" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D59" s="34" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E59" s="33" t="inlineStr">
+        <is>
+          <t>5.0%</t>
+        </is>
+      </c>
+      <c r="F59" s="34" t="n">
+        <v>52571</v>
+      </c>
+      <c r="G59" s="34" t="n">
+        <v>2759.9775</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="32" t="inlineStr">
+        <is>
+          <t>002949</t>
+        </is>
+      </c>
+      <c r="B60" s="32" t="inlineStr">
+        <is>
+          <t>"TUBO CONCRETO CII 15""</t>
+        </is>
+      </c>
+      <c r="C60" s="32" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D60" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F60" s="34" t="n">
+        <v>71618</v>
+      </c>
+      <c r="G60" s="34" t="n">
+        <v>71618</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MATERIALES:</t>
+        </is>
+      </c>
+      <c r="B61" s="36" t="n"/>
+      <c r="C61" s="36" t="n"/>
+      <c r="D61" s="36" t="n"/>
+      <c r="E61" s="36" t="n"/>
+      <c r="F61" s="36" t="n"/>
+      <c r="G61" s="42" t="n">
+        <v>74377.97749999999</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="43" t="inlineStr">
+        <is>
+          <t>COSTO DIRECTO:</t>
+        </is>
+      </c>
+      <c r="B62" s="44" t="n"/>
+      <c r="C62" s="44" t="n"/>
+      <c r="D62" s="44" t="n"/>
+      <c r="E62" s="44" t="n"/>
+      <c r="F62" s="44" t="n"/>
+      <c r="G62" s="45" t="n">
+        <v>91942.1575</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="46" t="inlineStr">
+        <is>
+          <t>COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B64" s="44" t="n"/>
+      <c r="C64" s="44" t="n"/>
+      <c r="D64" s="44" t="n"/>
+      <c r="E64" s="44" t="n"/>
+      <c r="F64" s="44" t="n"/>
+      <c r="G64" s="44" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="n"/>
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+      <c r="F65" s="23" t="inlineStr">
+        <is>
+          <t>514.34%</t>
+        </is>
+      </c>
+      <c r="G65" s="24" t="n">
+        <v>472892.2522109654</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="22" t="inlineStr">
+        <is>
+          <t>IMPREVISTOS</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G66" s="24" t="n">
+        <v>4597.107875000001</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="22" t="inlineStr">
+        <is>
+          <t>UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="n"/>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G67" s="24" t="n">
+        <v>4597.107875000001</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>IVA SOBRE LA UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+      <c r="F68" s="23" t="inlineStr">
+        <is>
+          <t>19.00%</t>
+        </is>
+      </c>
+      <c r="G68" s="24" t="n">
+        <v>17469.009925</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="23" t="inlineStr">
+        <is>
+          <t>525.29%</t>
+        </is>
+      </c>
+      <c r="G69" s="24" t="n">
+        <v>482959.9184572154</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="43" t="inlineStr">
+        <is>
+          <t>VALOR TOTAL ITEM:</t>
+        </is>
+      </c>
+      <c r="B70" s="44" t="n"/>
+      <c r="C70" s="44" t="n"/>
+      <c r="D70" s="44" t="n"/>
+      <c r="E70" s="44" t="n"/>
+      <c r="F70" s="44" t="n"/>
+      <c r="G70" s="45" t="n">
+        <v>574902.0759572154</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="40" t="inlineStr">
+        <is>
+          <t>02-03-16 - TUBERIA CONCRETO HR C II D=1.0 M</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="n"/>
+      <c r="C74" s="4" t="n"/>
+      <c r="D74" s="4" t="n"/>
+      <c r="E74" s="4" t="n"/>
+      <c r="F74" s="4" t="n"/>
+      <c r="G74" s="4" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>UNIDAD:</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ITEM:</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>02-03-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
+        <is>
+          <t>CÓDIGO RECURSO</t>
+        </is>
+      </c>
+      <c r="B76" s="31" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN</t>
+        </is>
+      </c>
+      <c r="C76" s="31" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D76" s="31" t="inlineStr">
+        <is>
+          <t>CANT.</t>
+        </is>
+      </c>
+      <c r="E76" s="31" t="inlineStr">
+        <is>
+          <t>DESP.%</t>
+        </is>
+      </c>
+      <c r="F76" s="31" t="inlineStr">
+        <is>
+          <t>PRECIO UNIT</t>
+        </is>
+      </c>
+      <c r="G76" s="31" t="inlineStr">
+        <is>
+          <t>VALOR PARCIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="32" t="inlineStr">
+        <is>
+          <t>--- MANO DE OBRA ---</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="n"/>
+      <c r="C77" s="4" t="n"/>
+      <c r="D77" s="4" t="n"/>
+      <c r="E77" s="4" t="n"/>
+      <c r="F77" s="4" t="n"/>
+      <c r="G77" s="4" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="32" t="inlineStr">
+        <is>
+          <t>MOAG12</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA ALBANILERIA 2 AYUDANTE-1 OFI</t>
+        </is>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D78" s="34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E78" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F78" s="34" t="n">
+        <v>32845</v>
+      </c>
+      <c r="G78" s="34" t="n">
+        <v>36129.5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="32" t="inlineStr">
+        <is>
+          <t>MOTO02</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA TOPOGRAFIA 2 CADENERO-1 TOP</t>
+        </is>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D79" s="34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E79" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F79" s="34" t="n">
+        <v>80691</v>
+      </c>
+      <c r="G79" s="34" t="n">
+        <v>32276.4</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MANO DE OBRA:</t>
+        </is>
+      </c>
+      <c r="B80" s="36" t="n"/>
+      <c r="C80" s="36" t="n"/>
+      <c r="D80" s="36" t="n"/>
+      <c r="E80" s="36" t="n"/>
+      <c r="F80" s="36" t="n"/>
+      <c r="G80" s="42" t="n">
+        <v>68405.89999999999</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="32" t="inlineStr">
+        <is>
+          <t>--- EQUIPO ---</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="n"/>
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="n"/>
+      <c r="E81" s="4" t="n"/>
+      <c r="F81" s="4" t="n"/>
+      <c r="G81" s="4" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="32" t="inlineStr">
+        <is>
+          <t>MQ0205</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="inlineStr">
+        <is>
+          <t>RETROEXCAVADORA JD-510</t>
+        </is>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="D82" s="34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E82" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F82" s="34" t="n">
+        <v>88000</v>
+      </c>
+      <c r="G82" s="34" t="n">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="32" t="inlineStr">
+        <is>
+          <t>MQ0301</t>
+        </is>
+      </c>
+      <c r="B83" s="32" t="inlineStr">
+        <is>
+          <t>HERRAMIENTA MENOR</t>
+        </is>
+      </c>
+      <c r="C83" s="32" t="inlineStr">
+        <is>
+          <t>GLB</t>
+        </is>
+      </c>
+      <c r="D83" s="34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E83" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F83" s="34" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G83" s="34" t="n">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL EQUIPO:</t>
+        </is>
+      </c>
+      <c r="B84" s="36" t="n"/>
+      <c r="C84" s="36" t="n"/>
+      <c r="D84" s="36" t="n"/>
+      <c r="E84" s="36" t="n"/>
+      <c r="F84" s="36" t="n"/>
+      <c r="G84" s="42" t="n">
+        <v>44480</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="32" t="inlineStr">
+        <is>
+          <t>--- MATERIALES ---</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="n"/>
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="32" t="inlineStr">
+        <is>
+          <t>001350</t>
+        </is>
+      </c>
+      <c r="B86" s="32" t="inlineStr">
+        <is>
+          <t>GRAVA TRITURADA.3/4</t>
+        </is>
+      </c>
+      <c r="C86" s="32" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D86" s="34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E86" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F86" s="34" t="n">
+        <v>52571</v>
+      </c>
+      <c r="G86" s="34" t="n">
+        <v>13142.75</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="32" t="inlineStr">
+        <is>
+          <t>005465</t>
+        </is>
+      </c>
+      <c r="B87" s="32" t="inlineStr">
+        <is>
+          <t>TUBO CONCRETO CII 1.0M HR</t>
+        </is>
+      </c>
+      <c r="C87" s="32" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D87" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" s="33" t="inlineStr">
+        <is>
+          <t>2.0%</t>
+        </is>
+      </c>
+      <c r="F87" s="34" t="n">
+        <v>319129</v>
+      </c>
+      <c r="G87" s="34" t="n">
+        <v>325511.58</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MATERIALES:</t>
+        </is>
+      </c>
+      <c r="B88" s="36" t="n"/>
+      <c r="C88" s="36" t="n"/>
+      <c r="D88" s="36" t="n"/>
+      <c r="E88" s="36" t="n"/>
+      <c r="F88" s="36" t="n"/>
+      <c r="G88" s="42" t="n">
+        <v>338654.33</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="43" t="inlineStr">
+        <is>
+          <t>COSTO DIRECTO:</t>
+        </is>
+      </c>
+      <c r="B89" s="44" t="n"/>
+      <c r="C89" s="44" t="n"/>
+      <c r="D89" s="44" t="n"/>
+      <c r="E89" s="44" t="n"/>
+      <c r="F89" s="44" t="n"/>
+      <c r="G89" s="45" t="n">
+        <v>451540.23</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="46" t="inlineStr">
+        <is>
+          <t>COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B91" s="44" t="n"/>
+      <c r="C91" s="44" t="n"/>
+      <c r="D91" s="44" t="n"/>
+      <c r="E91" s="44" t="n"/>
+      <c r="F91" s="44" t="n"/>
+      <c r="G91" s="44" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="22" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="n"/>
+      <c r="C92" s="4" t="n"/>
+      <c r="D92" s="4" t="n"/>
+      <c r="E92" s="4" t="n"/>
+      <c r="F92" s="23" t="inlineStr">
+        <is>
+          <t>514.34%</t>
+        </is>
+      </c>
+      <c r="G92" s="24" t="n">
+        <v>2322437.085822761</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="22" t="inlineStr">
+        <is>
+          <t>IMPREVISTOS</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="n"/>
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="4" t="n"/>
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G93" s="24" t="n">
+        <v>22577.0115</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="22" t="inlineStr">
+        <is>
+          <t>UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G94" s="24" t="n">
+        <v>22577.0115</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="22" t="inlineStr">
+        <is>
+          <t>IVA SOBRE LA UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="n"/>
+      <c r="C95" s="4" t="n"/>
+      <c r="D95" s="4" t="n"/>
+      <c r="E95" s="4" t="n"/>
+      <c r="F95" s="23" t="inlineStr">
+        <is>
+          <t>19.00%</t>
+        </is>
+      </c>
+      <c r="G95" s="24" t="n">
+        <v>85792.6437</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="n"/>
+      <c r="C96" s="4" t="n"/>
+      <c r="D96" s="4" t="n"/>
+      <c r="E96" s="4" t="n"/>
+      <c r="F96" s="23" t="inlineStr">
+        <is>
+          <t>525.29%</t>
+        </is>
+      </c>
+      <c r="G96" s="24" t="n">
+        <v>2371880.741007761</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="43" t="inlineStr">
+        <is>
+          <t>VALOR TOTAL ITEM:</t>
+        </is>
+      </c>
+      <c r="B97" s="44" t="n"/>
+      <c r="C97" s="44" t="n"/>
+      <c r="D97" s="44" t="n"/>
+      <c r="E97" s="44" t="n"/>
+      <c r="F97" s="44" t="n"/>
+      <c r="G97" s="45" t="n">
+        <v>2823420.971007761</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="40" t="inlineStr">
+        <is>
+          <t>02-04-25 - CAMARA INSPECCION TIPO I H=1.51-2.00 MTS</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="n"/>
+      <c r="C101" s="4" t="n"/>
+      <c r="D101" s="4" t="n"/>
+      <c r="E101" s="4" t="n"/>
+      <c r="F101" s="4" t="n"/>
+      <c r="G101" s="4" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>UNIDAD:</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>ITEM:</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>02-04-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="31" t="inlineStr">
+        <is>
+          <t>CÓDIGO RECURSO</t>
+        </is>
+      </c>
+      <c r="B103" s="31" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN</t>
+        </is>
+      </c>
+      <c r="C103" s="31" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D103" s="31" t="inlineStr">
+        <is>
+          <t>CANT.</t>
+        </is>
+      </c>
+      <c r="E103" s="31" t="inlineStr">
+        <is>
+          <t>DESP.%</t>
+        </is>
+      </c>
+      <c r="F103" s="31" t="inlineStr">
+        <is>
+          <t>PRECIO UNIT</t>
+        </is>
+      </c>
+      <c r="G103" s="31" t="inlineStr">
+        <is>
+          <t>VALOR PARCIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="32" t="inlineStr">
+        <is>
+          <t>--- MANO DE OBRA ---</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="n"/>
+      <c r="C104" s="4" t="n"/>
+      <c r="D104" s="4" t="n"/>
+      <c r="E104" s="4" t="n"/>
+      <c r="F104" s="4" t="n"/>
+      <c r="G104" s="4" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="32" t="inlineStr">
+        <is>
+          <t>MOAG12</t>
+        </is>
+      </c>
+      <c r="B105" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA ALBANILERIA2 AYUDANTE-1 OFI</t>
+        </is>
+      </c>
+      <c r="C105" s="32" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D105" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="E105" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F105" s="34" t="n">
+        <v>32845</v>
+      </c>
+      <c r="G105" s="34" t="n">
+        <v>394140</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MANO DE OBRA:</t>
+        </is>
+      </c>
+      <c r="B106" s="36" t="n"/>
+      <c r="C106" s="36" t="n"/>
+      <c r="D106" s="36" t="n"/>
+      <c r="E106" s="36" t="n"/>
+      <c r="F106" s="36" t="n"/>
+      <c r="G106" s="42" t="n">
+        <v>394140</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="32" t="inlineStr">
+        <is>
+          <t>--- MATERIALES ---</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="4" t="n"/>
+      <c r="D107" s="4" t="n"/>
+      <c r="E107" s="4" t="n"/>
+      <c r="F107" s="4" t="n"/>
+      <c r="G107" s="4" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="32" t="inlineStr">
+        <is>
+          <t>002556</t>
+        </is>
+      </c>
+      <c r="B108" s="32" t="inlineStr">
+        <is>
+          <t>TABLA 1x10x300 OTOBO</t>
+        </is>
+      </c>
+      <c r="C108" s="32" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D108" s="34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E108" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F108" s="34" t="n">
+        <v>13007</v>
+      </c>
+      <c r="G108" s="34" t="n">
+        <v>32517.5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="32" t="inlineStr">
+        <is>
+          <t>003890</t>
+        </is>
+      </c>
+      <c r="B109" s="32" t="inlineStr">
+        <is>
+          <t>FORMALETA CAMARA INSPECCIO</t>
+        </is>
+      </c>
+      <c r="C109" s="32" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D109" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E109" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F109" s="34" t="n">
+        <v>54213</v>
+      </c>
+      <c r="G109" s="34" t="n">
+        <v>108426</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="32" t="inlineStr">
+        <is>
+          <t>003999</t>
+        </is>
+      </c>
+      <c r="B110" s="32" t="inlineStr">
+        <is>
+          <t>HIERR.DE 60000 PSI 420 MPA</t>
+        </is>
+      </c>
+      <c r="C110" s="32" t="inlineStr">
+        <is>
+          <t>KLS</t>
+        </is>
+      </c>
+      <c r="D110" s="34" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="E110" s="33" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="F110" s="34" t="n">
+        <v>4287</v>
+      </c>
+      <c r="G110" s="34" t="n">
+        <v>293638.065</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="32" t="inlineStr">
+        <is>
+          <t>004600</t>
+        </is>
+      </c>
+      <c r="B111" s="32" t="inlineStr">
+        <is>
+          <t>HIERR.DE 37000 PSI 259 MPA</t>
+        </is>
+      </c>
+      <c r="C111" s="32" t="inlineStr">
+        <is>
+          <t>KLS</t>
+        </is>
+      </c>
+      <c r="D111" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="E111" s="33" t="inlineStr">
+        <is>
+          <t>3.0%</t>
+        </is>
+      </c>
+      <c r="F111" s="34" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G111" s="34" t="n">
+        <v>20600</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MATERIALES:</t>
+        </is>
+      </c>
+      <c r="B112" s="36" t="n"/>
+      <c r="C112" s="36" t="n"/>
+      <c r="D112" s="36" t="n"/>
+      <c r="E112" s="36" t="n"/>
+      <c r="F112" s="36" t="n"/>
+      <c r="G112" s="42" t="n">
+        <v>455181.565</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="43" t="inlineStr">
+        <is>
+          <t>COSTO DIRECTO:</t>
+        </is>
+      </c>
+      <c r="B113" s="44" t="n"/>
+      <c r="C113" s="44" t="n"/>
+      <c r="D113" s="44" t="n"/>
+      <c r="E113" s="44" t="n"/>
+      <c r="F113" s="44" t="n"/>
+      <c r="G113" s="45" t="n">
+        <v>849321.5649999999</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="46" t="inlineStr">
+        <is>
+          <t>COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B115" s="44" t="n"/>
+      <c r="C115" s="44" t="n"/>
+      <c r="D115" s="44" t="n"/>
+      <c r="E115" s="44" t="n"/>
+      <c r="F115" s="44" t="n"/>
+      <c r="G115" s="44" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="22" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="n"/>
+      <c r="C116" s="4" t="n"/>
+      <c r="D116" s="4" t="n"/>
+      <c r="E116" s="4" t="n"/>
+      <c r="F116" s="23" t="inlineStr">
+        <is>
+          <t>514.34%</t>
+        </is>
+      </c>
+      <c r="G116" s="24" t="n">
+        <v>4368372.448995356</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="22" t="inlineStr">
+        <is>
+          <t>IMPREVISTOS</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="n"/>
+      <c r="C117" s="4" t="n"/>
+      <c r="D117" s="4" t="n"/>
+      <c r="E117" s="4" t="n"/>
+      <c r="F117" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G117" s="24" t="n">
+        <v>42466.07825</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="22" t="inlineStr">
+        <is>
+          <t>UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="n"/>
+      <c r="C118" s="4" t="n"/>
+      <c r="D118" s="4" t="n"/>
+      <c r="E118" s="4" t="n"/>
+      <c r="F118" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G118" s="24" t="n">
+        <v>42466.07825</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="22" t="inlineStr">
+        <is>
+          <t>IVA SOBRE LA UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="n"/>
+      <c r="C119" s="4" t="n"/>
+      <c r="D119" s="4" t="n"/>
+      <c r="E119" s="4" t="n"/>
+      <c r="F119" s="23" t="inlineStr">
+        <is>
+          <t>19.00%</t>
+        </is>
+      </c>
+      <c r="G119" s="24" t="n">
+        <v>161371.09735</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="n"/>
+      <c r="C120" s="4" t="n"/>
+      <c r="D120" s="4" t="n"/>
+      <c r="E120" s="4" t="n"/>
+      <c r="F120" s="23" t="inlineStr">
+        <is>
+          <t>525.29%</t>
+        </is>
+      </c>
+      <c r="G120" s="24" t="n">
+        <v>4461373.160362856</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="43" t="inlineStr">
+        <is>
+          <t>VALOR TOTAL ITEM:</t>
+        </is>
+      </c>
+      <c r="B121" s="44" t="n"/>
+      <c r="C121" s="44" t="n"/>
+      <c r="D121" s="44" t="n"/>
+      <c r="E121" s="44" t="n"/>
+      <c r="F121" s="44" t="n"/>
+      <c r="G121" s="45" t="n">
+        <v>5310694.725362856</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="40" t="inlineStr">
+        <is>
+          <t>02-06-04 - VALVULA CHAPALETA Q=4.10L/SEG S=1.5M 10"</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="n"/>
+      <c r="C125" s="4" t="n"/>
+      <c r="D125" s="4" t="n"/>
+      <c r="E125" s="4" t="n"/>
+      <c r="F125" s="4" t="n"/>
+      <c r="G125" s="4" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>UNIDAD:</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ITEM:</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>02-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="31" t="inlineStr">
+        <is>
+          <t>CÓDIGO RECURSO</t>
+        </is>
+      </c>
+      <c r="B127" s="31" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN</t>
+        </is>
+      </c>
+      <c r="C127" s="31" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D127" s="31" t="inlineStr">
+        <is>
+          <t>CANT.</t>
+        </is>
+      </c>
+      <c r="E127" s="31" t="inlineStr">
+        <is>
+          <t>DESP.%</t>
+        </is>
+      </c>
+      <c r="F127" s="31" t="inlineStr">
+        <is>
+          <t>PRECIO UNIT</t>
+        </is>
+      </c>
+      <c r="G127" s="31" t="inlineStr">
+        <is>
+          <t>VALOR PARCIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="32" t="inlineStr">
+        <is>
+          <t>--- MANO DE OBRA ---</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="n"/>
+      <c r="C128" s="4" t="n"/>
+      <c r="D128" s="4" t="n"/>
+      <c r="E128" s="4" t="n"/>
+      <c r="F128" s="4" t="n"/>
+      <c r="G128" s="4" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="32" t="inlineStr">
+        <is>
+          <t>MOAG02</t>
+        </is>
+      </c>
+      <c r="B129" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA ALBANILERIA2 AYUDANTE</t>
+        </is>
+      </c>
+      <c r="C129" s="32" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D129" s="34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E129" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F129" s="34" t="n">
+        <v>17897</v>
+      </c>
+      <c r="G129" s="34" t="n">
+        <v>8948.5</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="32" t="inlineStr">
+        <is>
+          <t>MOIS01</t>
+        </is>
+      </c>
+      <c r="B130" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA HIDROSANIT.1 AYUDANTE-1 OFI</t>
+        </is>
+      </c>
+      <c r="C130" s="32" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D130" s="34" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E130" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F130" s="34" t="n">
+        <v>25391</v>
+      </c>
+      <c r="G130" s="34" t="n">
+        <v>13203.32</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MANO DE OBRA:</t>
+        </is>
+      </c>
+      <c r="B131" s="36" t="n"/>
+      <c r="C131" s="36" t="n"/>
+      <c r="D131" s="36" t="n"/>
+      <c r="E131" s="36" t="n"/>
+      <c r="F131" s="36" t="n"/>
+      <c r="G131" s="42" t="n">
+        <v>22151.82</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="32" t="inlineStr">
+        <is>
+          <t>--- MATERIALES ---</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="n"/>
+      <c r="C132" s="4" t="n"/>
+      <c r="D132" s="4" t="n"/>
+      <c r="E132" s="4" t="n"/>
+      <c r="F132" s="4" t="n"/>
+      <c r="G132" s="4" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="32" t="inlineStr">
+        <is>
+          <t>000507</t>
+        </is>
+      </c>
+      <c r="B133" s="32" t="inlineStr">
+        <is>
+          <t>"VAL CHAPAL Q=4.1LT/S D10"</t>
+        </is>
+      </c>
+      <c r="C133" s="32" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D133" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F133" s="34" t="n">
+        <v>2217920</v>
+      </c>
+      <c r="G133" s="34" t="n">
+        <v>2217920</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MATERIALES:</t>
+        </is>
+      </c>
+      <c r="B134" s="36" t="n"/>
+      <c r="C134" s="36" t="n"/>
+      <c r="D134" s="36" t="n"/>
+      <c r="E134" s="36" t="n"/>
+      <c r="F134" s="36" t="n"/>
+      <c r="G134" s="42" t="n">
+        <v>2217920</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="43" t="inlineStr">
+        <is>
+          <t>COSTO DIRECTO:</t>
+        </is>
+      </c>
+      <c r="B135" s="44" t="n"/>
+      <c r="C135" s="44" t="n"/>
+      <c r="D135" s="44" t="n"/>
+      <c r="E135" s="44" t="n"/>
+      <c r="F135" s="44" t="n"/>
+      <c r="G135" s="45" t="n">
+        <v>2240071.82</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="46" t="inlineStr">
+        <is>
+          <t>COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B137" s="44" t="n"/>
+      <c r="C137" s="44" t="n"/>
+      <c r="D137" s="44" t="n"/>
+      <c r="E137" s="44" t="n"/>
+      <c r="F137" s="44" t="n"/>
+      <c r="G137" s="44" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="22" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="n"/>
+      <c r="C138" s="4" t="n"/>
+      <c r="D138" s="4" t="n"/>
+      <c r="E138" s="4" t="n"/>
+      <c r="F138" s="23" t="inlineStr">
+        <is>
+          <t>514.34%</t>
+        </is>
+      </c>
+      <c r="G138" s="24" t="n">
+        <v>11521511.31622201</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="22" t="inlineStr">
+        <is>
+          <t>IMPREVISTOS</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="n"/>
+      <c r="C139" s="4" t="n"/>
+      <c r="D139" s="4" t="n"/>
+      <c r="E139" s="4" t="n"/>
+      <c r="F139" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G139" s="24" t="n">
+        <v>112003.591</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="22" t="inlineStr">
+        <is>
+          <t>UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="n"/>
+      <c r="C140" s="4" t="n"/>
+      <c r="D140" s="4" t="n"/>
+      <c r="E140" s="4" t="n"/>
+      <c r="F140" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G140" s="24" t="n">
+        <v>112003.591</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="22" t="inlineStr">
+        <is>
+          <t>IVA SOBRE LA UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="n"/>
+      <c r="C141" s="4" t="n"/>
+      <c r="D141" s="4" t="n"/>
+      <c r="E141" s="4" t="n"/>
+      <c r="F141" s="23" t="inlineStr">
+        <is>
+          <t>19.00%</t>
+        </is>
+      </c>
+      <c r="G141" s="24" t="n">
+        <v>425613.6458</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="n"/>
+      <c r="C142" s="4" t="n"/>
+      <c r="D142" s="4" t="n"/>
+      <c r="E142" s="4" t="n"/>
+      <c r="F142" s="23" t="inlineStr">
+        <is>
+          <t>525.29%</t>
+        </is>
+      </c>
+      <c r="G142" s="24" t="n">
+        <v>11766799.18051201</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="43" t="inlineStr">
+        <is>
+          <t>VALOR TOTAL ITEM:</t>
+        </is>
+      </c>
+      <c r="B143" s="44" t="n"/>
+      <c r="C143" s="44" t="n"/>
+      <c r="D143" s="44" t="n"/>
+      <c r="E143" s="44" t="n"/>
+      <c r="F143" s="44" t="n"/>
+      <c r="G143" s="45" t="n">
+        <v>14006871.00051201</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="40" t="inlineStr">
+        <is>
+          <t>02-07-08 - TUB PVC NOVAFORT 12"</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="n"/>
+      <c r="C147" s="4" t="n"/>
+      <c r="D147" s="4" t="n"/>
+      <c r="E147" s="4" t="n"/>
+      <c r="F147" s="4" t="n"/>
+      <c r="G147" s="4" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>UNIDAD:</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>ITEM:</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>02-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="31" t="inlineStr">
+        <is>
+          <t>CÓDIGO RECURSO</t>
+        </is>
+      </c>
+      <c r="B149" s="31" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN</t>
+        </is>
+      </c>
+      <c r="C149" s="31" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D149" s="31" t="inlineStr">
+        <is>
+          <t>CANT.</t>
+        </is>
+      </c>
+      <c r="E149" s="31" t="inlineStr">
+        <is>
+          <t>DESP.%</t>
+        </is>
+      </c>
+      <c r="F149" s="31" t="inlineStr">
+        <is>
+          <t>PRECIO UNIT</t>
+        </is>
+      </c>
+      <c r="G149" s="31" t="inlineStr">
+        <is>
+          <t>VALOR PARCIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="32" t="inlineStr">
+        <is>
+          <t>--- MANO DE OBRA ---</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="n"/>
+      <c r="C150" s="4" t="n"/>
+      <c r="D150" s="4" t="n"/>
+      <c r="E150" s="4" t="n"/>
+      <c r="F150" s="4" t="n"/>
+      <c r="G150" s="4" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="32" t="inlineStr">
+        <is>
+          <t>MOAG02</t>
+        </is>
+      </c>
+      <c r="B151" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA ALBANILERIA2 AYUDANTE</t>
+        </is>
+      </c>
+      <c r="C151" s="32" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D151" s="34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E151" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F151" s="34" t="n">
+        <v>17897</v>
+      </c>
+      <c r="G151" s="34" t="n">
+        <v>5369.099999999999</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="32" t="inlineStr">
+        <is>
+          <t>MOIS01</t>
+        </is>
+      </c>
+      <c r="B152" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA HIDROSANIT.1 AYUDANTE-1 OFI</t>
+        </is>
+      </c>
+      <c r="C152" s="32" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D152" s="34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E152" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F152" s="34" t="n">
+        <v>25391</v>
+      </c>
+      <c r="G152" s="34" t="n">
+        <v>10156.4</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MANO DE OBRA:</t>
+        </is>
+      </c>
+      <c r="B153" s="36" t="n"/>
+      <c r="C153" s="36" t="n"/>
+      <c r="D153" s="36" t="n"/>
+      <c r="E153" s="36" t="n"/>
+      <c r="F153" s="36" t="n"/>
+      <c r="G153" s="42" t="n">
+        <v>15525.5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="32" t="inlineStr">
+        <is>
+          <t>--- MATERIALES ---</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="n"/>
+      <c r="C154" s="4" t="n"/>
+      <c r="D154" s="4" t="n"/>
+      <c r="E154" s="4" t="n"/>
+      <c r="F154" s="4" t="n"/>
+      <c r="G154" s="4" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="32" t="inlineStr">
+        <is>
+          <t>000191</t>
+        </is>
+      </c>
+      <c r="B155" s="32" t="inlineStr">
+        <is>
+          <t>"TUBO SAN 12""PVC-315M</t>
+        </is>
+      </c>
+      <c r="C155" s="32" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D155" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F155" s="34" t="n">
+        <v>116106</v>
+      </c>
+      <c r="G155" s="34" t="n">
+        <v>116106</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="32" t="inlineStr">
+        <is>
+          <t>000242</t>
+        </is>
+      </c>
+      <c r="B156" s="32" t="inlineStr">
+        <is>
+          <t>HIDROSELLO NOVAFORT 315MM</t>
+        </is>
+      </c>
+      <c r="C156" s="32" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D156" s="34" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E156" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F156" s="34" t="n">
+        <v>31766</v>
+      </c>
+      <c r="G156" s="34" t="n">
+        <v>10482.78</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="32" t="inlineStr">
+        <is>
+          <t>000521</t>
+        </is>
+      </c>
+      <c r="B157" s="32" t="inlineStr">
+        <is>
+          <t>ADHESIVO NOVAFORT</t>
+        </is>
+      </c>
+      <c r="C157" s="32" t="inlineStr">
+        <is>
+          <t>GLN</t>
+        </is>
+      </c>
+      <c r="D157" s="34" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E157" s="33" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+      <c r="F157" s="34" t="n">
+        <v>86557</v>
+      </c>
+      <c r="G157" s="34" t="n">
+        <v>262.26771</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="32" t="inlineStr">
+        <is>
+          <t>000522</t>
+        </is>
+      </c>
+      <c r="B158" s="32" t="inlineStr">
+        <is>
+          <t>ACONDICION SUPERF NOVAFORT</t>
+        </is>
+      </c>
+      <c r="C158" s="32" t="inlineStr">
+        <is>
+          <t>GLN</t>
+        </is>
+      </c>
+      <c r="D158" s="34" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E158" s="33" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+      <c r="F158" s="34" t="n">
+        <v>100962</v>
+      </c>
+      <c r="G158" s="34" t="n">
+        <v>305.91486</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MATERIALES:</t>
+        </is>
+      </c>
+      <c r="B159" s="36" t="n"/>
+      <c r="C159" s="36" t="n"/>
+      <c r="D159" s="36" t="n"/>
+      <c r="E159" s="36" t="n"/>
+      <c r="F159" s="36" t="n"/>
+      <c r="G159" s="42" t="n">
+        <v>127156.96257</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="43" t="inlineStr">
+        <is>
+          <t>COSTO DIRECTO:</t>
+        </is>
+      </c>
+      <c r="B160" s="44" t="n"/>
+      <c r="C160" s="44" t="n"/>
+      <c r="D160" s="44" t="n"/>
+      <c r="E160" s="44" t="n"/>
+      <c r="F160" s="44" t="n"/>
+      <c r="G160" s="45" t="n">
+        <v>142682.46257</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="46" t="inlineStr">
+        <is>
+          <t>COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B162" s="44" t="n"/>
+      <c r="C162" s="44" t="n"/>
+      <c r="D162" s="44" t="n"/>
+      <c r="E162" s="44" t="n"/>
+      <c r="F162" s="44" t="n"/>
+      <c r="G162" s="44" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="22" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="n"/>
+      <c r="C163" s="4" t="n"/>
+      <c r="D163" s="4" t="n"/>
+      <c r="E163" s="4" t="n"/>
+      <c r="F163" s="23" t="inlineStr">
+        <is>
+          <t>514.34%</t>
+        </is>
+      </c>
+      <c r="G163" s="24" t="n">
+        <v>733868.2592447764</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="22" t="inlineStr">
+        <is>
+          <t>IMPREVISTOS</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="n"/>
+      <c r="C164" s="4" t="n"/>
+      <c r="D164" s="4" t="n"/>
+      <c r="E164" s="4" t="n"/>
+      <c r="F164" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G164" s="24" t="n">
+        <v>7134.1231285</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="22" t="inlineStr">
+        <is>
+          <t>UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="n"/>
+      <c r="C165" s="4" t="n"/>
+      <c r="D165" s="4" t="n"/>
+      <c r="E165" s="4" t="n"/>
+      <c r="F165" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G165" s="24" t="n">
+        <v>7134.1231285</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="22" t="inlineStr">
+        <is>
+          <t>IVA SOBRE LA UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="n"/>
+      <c r="C166" s="4" t="n"/>
+      <c r="D166" s="4" t="n"/>
+      <c r="E166" s="4" t="n"/>
+      <c r="F166" s="23" t="inlineStr">
+        <is>
+          <t>19.00%</t>
+        </is>
+      </c>
+      <c r="G166" s="24" t="n">
+        <v>27109.6678883</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="n"/>
+      <c r="C167" s="4" t="n"/>
+      <c r="D167" s="4" t="n"/>
+      <c r="E167" s="4" t="n"/>
+      <c r="F167" s="23" t="inlineStr">
+        <is>
+          <t>525.29%</t>
+        </is>
+      </c>
+      <c r="G167" s="24" t="n">
+        <v>749491.9888961915</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="43" t="inlineStr">
+        <is>
+          <t>VALOR TOTAL ITEM:</t>
+        </is>
+      </c>
+      <c r="B168" s="44" t="n"/>
+      <c r="C168" s="44" t="n"/>
+      <c r="D168" s="44" t="n"/>
+      <c r="E168" s="44" t="n"/>
+      <c r="F168" s="44" t="n"/>
+      <c r="G168" s="45" t="n">
+        <v>892174.4514661914</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="40" t="inlineStr">
+        <is>
+          <t>03-01-04 - MOTOR ELEC 25HP 3600 RPM BOMBA</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="n"/>
+      <c r="C172" s="4" t="n"/>
+      <c r="D172" s="4" t="n"/>
+      <c r="E172" s="4" t="n"/>
+      <c r="F172" s="4" t="n"/>
+      <c r="G172" s="4" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>UNIDAD:</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>ITEM:</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>03-01-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="31" t="inlineStr">
+        <is>
+          <t>CÓDIGO RECURSO</t>
+        </is>
+      </c>
+      <c r="B174" s="31" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN</t>
+        </is>
+      </c>
+      <c r="C174" s="31" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D174" s="31" t="inlineStr">
+        <is>
+          <t>CANT.</t>
+        </is>
+      </c>
+      <c r="E174" s="31" t="inlineStr">
+        <is>
+          <t>DESP.%</t>
+        </is>
+      </c>
+      <c r="F174" s="31" t="inlineStr">
+        <is>
+          <t>PRECIO UNIT</t>
+        </is>
+      </c>
+      <c r="G174" s="31" t="inlineStr">
+        <is>
+          <t>VALOR PARCIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="32" t="inlineStr">
+        <is>
+          <t>--- MANO DE OBRA ---</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="n"/>
+      <c r="C175" s="4" t="n"/>
+      <c r="D175" s="4" t="n"/>
+      <c r="E175" s="4" t="n"/>
+      <c r="F175" s="4" t="n"/>
+      <c r="G175" s="4" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="32" t="inlineStr">
+        <is>
+          <t>MOIS01</t>
+        </is>
+      </c>
+      <c r="B176" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA HIDROSANIT.1 AYUDANTE-1 OFI</t>
+        </is>
+      </c>
+      <c r="C176" s="32" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D176" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E176" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F176" s="34" t="n">
+        <v>25391</v>
+      </c>
+      <c r="G176" s="34" t="n">
+        <v>101564</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MANO DE OBRA:</t>
+        </is>
+      </c>
+      <c r="B177" s="36" t="n"/>
+      <c r="C177" s="36" t="n"/>
+      <c r="D177" s="36" t="n"/>
+      <c r="E177" s="36" t="n"/>
+      <c r="F177" s="36" t="n"/>
+      <c r="G177" s="42" t="n">
+        <v>101564</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="32" t="inlineStr">
+        <is>
+          <t>--- EQUIPO ---</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="n"/>
+      <c r="C178" s="4" t="n"/>
+      <c r="D178" s="4" t="n"/>
+      <c r="E178" s="4" t="n"/>
+      <c r="F178" s="4" t="n"/>
+      <c r="G178" s="4" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="32" t="inlineStr">
+        <is>
+          <t>MQ0301</t>
+        </is>
+      </c>
+      <c r="B179" s="32" t="inlineStr">
+        <is>
+          <t>HERRAMIENTA MENOR</t>
+        </is>
+      </c>
+      <c r="C179" s="32" t="inlineStr">
+        <is>
+          <t>GLB</t>
+        </is>
+      </c>
+      <c r="D179" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E179" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F179" s="34" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G179" s="34" t="n">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL EQUIPO:</t>
+        </is>
+      </c>
+      <c r="B180" s="36" t="n"/>
+      <c r="C180" s="36" t="n"/>
+      <c r="D180" s="36" t="n"/>
+      <c r="E180" s="36" t="n"/>
+      <c r="F180" s="36" t="n"/>
+      <c r="G180" s="42" t="n">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="32" t="inlineStr">
+        <is>
+          <t>--- MATERIALES ---</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="n"/>
+      <c r="C181" s="4" t="n"/>
+      <c r="D181" s="4" t="n"/>
+      <c r="E181" s="4" t="n"/>
+      <c r="F181" s="4" t="n"/>
+      <c r="G181" s="4" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="32" t="inlineStr">
+        <is>
+          <t>004905</t>
+        </is>
+      </c>
+      <c r="B182" s="32" t="inlineStr">
+        <is>
+          <t>MOTOR EL.BOMB 25HP</t>
+        </is>
+      </c>
+      <c r="C182" s="32" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D182" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F182" s="34" t="n">
+        <v>2779650</v>
+      </c>
+      <c r="G182" s="34" t="n">
+        <v>2779650</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MATERIALES:</t>
+        </is>
+      </c>
+      <c r="B183" s="36" t="n"/>
+      <c r="C183" s="36" t="n"/>
+      <c r="D183" s="36" t="n"/>
+      <c r="E183" s="36" t="n"/>
+      <c r="F183" s="36" t="n"/>
+      <c r="G183" s="42" t="n">
+        <v>2779650</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="43" t="inlineStr">
+        <is>
+          <t>COSTO DIRECTO:</t>
+        </is>
+      </c>
+      <c r="B184" s="44" t="n"/>
+      <c r="C184" s="44" t="n"/>
+      <c r="D184" s="44" t="n"/>
+      <c r="E184" s="44" t="n"/>
+      <c r="F184" s="44" t="n"/>
+      <c r="G184" s="45" t="n">
+        <v>2884414</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="46" t="inlineStr">
+        <is>
+          <t>COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B186" s="44" t="n"/>
+      <c r="C186" s="44" t="n"/>
+      <c r="D186" s="44" t="n"/>
+      <c r="E186" s="44" t="n"/>
+      <c r="F186" s="44" t="n"/>
+      <c r="G186" s="44" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="22" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="n"/>
+      <c r="C187" s="4" t="n"/>
+      <c r="D187" s="4" t="n"/>
+      <c r="E187" s="4" t="n"/>
+      <c r="F187" s="23" t="inlineStr">
+        <is>
+          <t>514.34%</t>
+        </is>
+      </c>
+      <c r="G187" s="24" t="n">
+        <v>14835599.57540522</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="22" t="inlineStr">
+        <is>
+          <t>IMPREVISTOS</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="n"/>
+      <c r="C188" s="4" t="n"/>
+      <c r="D188" s="4" t="n"/>
+      <c r="E188" s="4" t="n"/>
+      <c r="F188" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G188" s="24" t="n">
+        <v>144220.7</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="22" t="inlineStr">
+        <is>
+          <t>UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="n"/>
+      <c r="C189" s="4" t="n"/>
+      <c r="D189" s="4" t="n"/>
+      <c r="E189" s="4" t="n"/>
+      <c r="F189" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G189" s="24" t="n">
+        <v>144220.7</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="22" t="inlineStr">
+        <is>
+          <t>IVA SOBRE LA UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="n"/>
+      <c r="C190" s="4" t="n"/>
+      <c r="D190" s="4" t="n"/>
+      <c r="E190" s="4" t="n"/>
+      <c r="F190" s="23" t="inlineStr">
+        <is>
+          <t>19.00%</t>
+        </is>
+      </c>
+      <c r="G190" s="24" t="n">
+        <v>548038.66</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="n"/>
+      <c r="C191" s="4" t="n"/>
+      <c r="D191" s="4" t="n"/>
+      <c r="E191" s="4" t="n"/>
+      <c r="F191" s="23" t="inlineStr">
+        <is>
+          <t>525.29%</t>
+        </is>
+      </c>
+      <c r="G191" s="24" t="n">
+        <v>15151442.90840521</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="43" t="inlineStr">
+        <is>
+          <t>VALOR TOTAL ITEM:</t>
+        </is>
+      </c>
+      <c r="B192" s="44" t="n"/>
+      <c r="C192" s="44" t="n"/>
+      <c r="D192" s="44" t="n"/>
+      <c r="E192" s="44" t="n"/>
+      <c r="F192" s="44" t="n"/>
+      <c r="G192" s="45" t="n">
+        <v>18035856.90840521</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="40" t="inlineStr">
+        <is>
+          <t>03-02-09 - BOMBA SUMERG1.0 HP LAPICERO 4" BRONCE</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="n"/>
+      <c r="C196" s="4" t="n"/>
+      <c r="D196" s="4" t="n"/>
+      <c r="E196" s="4" t="n"/>
+      <c r="F196" s="4" t="n"/>
+      <c r="G196" s="4" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>UNIDAD:</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>ITEM:</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>03-02-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="31" t="inlineStr">
+        <is>
+          <t>CÓDIGO RECURSO</t>
+        </is>
+      </c>
+      <c r="B198" s="31" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN</t>
+        </is>
+      </c>
+      <c r="C198" s="31" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D198" s="31" t="inlineStr">
+        <is>
+          <t>CANT.</t>
+        </is>
+      </c>
+      <c r="E198" s="31" t="inlineStr">
+        <is>
+          <t>DESP.%</t>
+        </is>
+      </c>
+      <c r="F198" s="31" t="inlineStr">
+        <is>
+          <t>PRECIO UNIT</t>
+        </is>
+      </c>
+      <c r="G198" s="31" t="inlineStr">
+        <is>
+          <t>VALOR PARCIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="32" t="inlineStr">
+        <is>
+          <t>--- MANO DE OBRA ---</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="n"/>
+      <c r="C199" s="4" t="n"/>
+      <c r="D199" s="4" t="n"/>
+      <c r="E199" s="4" t="n"/>
+      <c r="F199" s="4" t="n"/>
+      <c r="G199" s="4" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="32" t="inlineStr">
+        <is>
+          <t>MOIE01</t>
+        </is>
+      </c>
+      <c r="B200" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA ELECTRICAS1 AYUDANTE-1 OFI</t>
+        </is>
+      </c>
+      <c r="C200" s="32" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D200" s="34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E200" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F200" s="34" t="n">
+        <v>33455</v>
+      </c>
+      <c r="G200" s="34" t="n">
+        <v>83637.5</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="32" t="inlineStr">
+        <is>
+          <t>MOIS01</t>
+        </is>
+      </c>
+      <c r="B201" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA HIDROSANIT.1 AYUDANTE-1 OFI</t>
+        </is>
+      </c>
+      <c r="C201" s="32" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D201" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E201" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F201" s="34" t="n">
+        <v>25391</v>
+      </c>
+      <c r="G201" s="34" t="n">
+        <v>76173</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MANO DE OBRA:</t>
+        </is>
+      </c>
+      <c r="B202" s="36" t="n"/>
+      <c r="C202" s="36" t="n"/>
+      <c r="D202" s="36" t="n"/>
+      <c r="E202" s="36" t="n"/>
+      <c r="F202" s="36" t="n"/>
+      <c r="G202" s="42" t="n">
+        <v>159810.5</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="32" t="inlineStr">
+        <is>
+          <t>--- EQUIPO ---</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="n"/>
+      <c r="C203" s="4" t="n"/>
+      <c r="D203" s="4" t="n"/>
+      <c r="E203" s="4" t="n"/>
+      <c r="F203" s="4" t="n"/>
+      <c r="G203" s="4" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="32" t="inlineStr">
+        <is>
+          <t>MQ0301</t>
+        </is>
+      </c>
+      <c r="B204" s="32" t="inlineStr">
+        <is>
+          <t>HERRAMIENTA MENOR</t>
+        </is>
+      </c>
+      <c r="C204" s="32" t="inlineStr">
+        <is>
+          <t>GLB</t>
+        </is>
+      </c>
+      <c r="D204" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E204" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F204" s="34" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G204" s="34" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL EQUIPO:</t>
+        </is>
+      </c>
+      <c r="B205" s="36" t="n"/>
+      <c r="C205" s="36" t="n"/>
+      <c r="D205" s="36" t="n"/>
+      <c r="E205" s="36" t="n"/>
+      <c r="F205" s="36" t="n"/>
+      <c r="G205" s="42" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="32" t="inlineStr">
+        <is>
+          <t>--- MATERIALES ---</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="n"/>
+      <c r="C206" s="4" t="n"/>
+      <c r="D206" s="4" t="n"/>
+      <c r="E206" s="4" t="n"/>
+      <c r="F206" s="4" t="n"/>
+      <c r="G206" s="4" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="32" t="inlineStr">
+        <is>
+          <t>000999</t>
+        </is>
+      </c>
+      <c r="B207" s="32" t="inlineStr">
+        <is>
+          <t>BOM.SUM. 1 HP</t>
+        </is>
+      </c>
+      <c r="C207" s="32" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D207" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F207" s="34" t="n">
+        <v>2593766</v>
+      </c>
+      <c r="G207" s="34" t="n">
+        <v>2593766</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MATERIALES:</t>
+        </is>
+      </c>
+      <c r="B208" s="36" t="n"/>
+      <c r="C208" s="36" t="n"/>
+      <c r="D208" s="36" t="n"/>
+      <c r="E208" s="36" t="n"/>
+      <c r="F208" s="36" t="n"/>
+      <c r="G208" s="42" t="n">
+        <v>2593766</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="43" t="inlineStr">
+        <is>
+          <t>COSTO DIRECTO:</t>
+        </is>
+      </c>
+      <c r="B209" s="44" t="n"/>
+      <c r="C209" s="44" t="n"/>
+      <c r="D209" s="44" t="n"/>
+      <c r="E209" s="44" t="n"/>
+      <c r="F209" s="44" t="n"/>
+      <c r="G209" s="45" t="n">
+        <v>2758376.5</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="46" t="inlineStr">
+        <is>
+          <t>COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B211" s="44" t="n"/>
+      <c r="C211" s="44" t="n"/>
+      <c r="D211" s="44" t="n"/>
+      <c r="E211" s="44" t="n"/>
+      <c r="F211" s="44" t="n"/>
+      <c r="G211" s="44" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="22" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="n"/>
+      <c r="C212" s="4" t="n"/>
+      <c r="D212" s="4" t="n"/>
+      <c r="E212" s="4" t="n"/>
+      <c r="F212" s="23" t="inlineStr">
+        <is>
+          <t>514.34%</t>
+        </is>
+      </c>
+      <c r="G212" s="24" t="n">
+        <v>14187342.46616738</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="22" t="inlineStr">
+        <is>
+          <t>IMPREVISTOS</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="n"/>
+      <c r="C213" s="4" t="n"/>
+      <c r="D213" s="4" t="n"/>
+      <c r="E213" s="4" t="n"/>
+      <c r="F213" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G213" s="24" t="n">
+        <v>137918.825</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="22" t="inlineStr">
+        <is>
+          <t>UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="n"/>
+      <c r="C214" s="4" t="n"/>
+      <c r="D214" s="4" t="n"/>
+      <c r="E214" s="4" t="n"/>
+      <c r="F214" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G214" s="24" t="n">
+        <v>137918.825</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="22" t="inlineStr">
+        <is>
+          <t>IVA SOBRE LA UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="n"/>
+      <c r="C215" s="4" t="n"/>
+      <c r="D215" s="4" t="n"/>
+      <c r="E215" s="4" t="n"/>
+      <c r="F215" s="23" t="inlineStr">
+        <is>
+          <t>19.00%</t>
+        </is>
+      </c>
+      <c r="G215" s="24" t="n">
+        <v>524091.535</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="n"/>
+      <c r="C216" s="4" t="n"/>
+      <c r="D216" s="4" t="n"/>
+      <c r="E216" s="4" t="n"/>
+      <c r="F216" s="23" t="inlineStr">
+        <is>
+          <t>525.29%</t>
+        </is>
+      </c>
+      <c r="G216" s="24" t="n">
+        <v>14489384.69291738</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="43" t="inlineStr">
+        <is>
+          <t>VALOR TOTAL ITEM:</t>
+        </is>
+      </c>
+      <c r="B217" s="44" t="n"/>
+      <c r="C217" s="44" t="n"/>
+      <c r="D217" s="44" t="n"/>
+      <c r="E217" s="44" t="n"/>
+      <c r="F217" s="44" t="n"/>
+      <c r="G217" s="45" t="n">
+        <v>17247761.19291738</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="40" t="inlineStr">
+        <is>
+          <t>04-01-62 - REJILLA HIERRO D=1/2" E=1/2 1.50x.40MTS</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="n"/>
+      <c r="C221" s="4" t="n"/>
+      <c r="D221" s="4" t="n"/>
+      <c r="E221" s="4" t="n"/>
+      <c r="F221" s="4" t="n"/>
+      <c r="G221" s="4" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>UNIDAD:</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>ITEM:</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>04-01-62</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="31" t="inlineStr">
+        <is>
+          <t>CÓDIGO RECURSO</t>
+        </is>
+      </c>
+      <c r="B223" s="31" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN</t>
+        </is>
+      </c>
+      <c r="C223" s="31" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D223" s="31" t="inlineStr">
+        <is>
+          <t>CANT.</t>
+        </is>
+      </c>
+      <c r="E223" s="31" t="inlineStr">
+        <is>
+          <t>DESP.%</t>
+        </is>
+      </c>
+      <c r="F223" s="31" t="inlineStr">
+        <is>
+          <t>PRECIO UNIT</t>
+        </is>
+      </c>
+      <c r="G223" s="31" t="inlineStr">
+        <is>
+          <t>VALOR PARCIAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="32" t="inlineStr">
+        <is>
+          <t>--- MANO DE OBRA ---</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="n"/>
+      <c r="C224" s="4" t="n"/>
+      <c r="D224" s="4" t="n"/>
+      <c r="E224" s="4" t="n"/>
+      <c r="F224" s="4" t="n"/>
+      <c r="G224" s="4" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="32" t="inlineStr">
+        <is>
+          <t>MOIS01</t>
+        </is>
+      </c>
+      <c r="B225" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA HIDROSANIT.1 AYUDANTE-1 OFI</t>
+        </is>
+      </c>
+      <c r="C225" s="32" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="D225" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F225" s="34" t="n">
+        <v>25391</v>
+      </c>
+      <c r="G225" s="34" t="n">
+        <v>25391</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MANO DE OBRA:</t>
+        </is>
+      </c>
+      <c r="B226" s="36" t="n"/>
+      <c r="C226" s="36" t="n"/>
+      <c r="D226" s="36" t="n"/>
+      <c r="E226" s="36" t="n"/>
+      <c r="F226" s="36" t="n"/>
+      <c r="G226" s="42" t="n">
+        <v>25391</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="32" t="inlineStr">
+        <is>
+          <t>--- EQUIPO ---</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="n"/>
+      <c r="C227" s="4" t="n"/>
+      <c r="D227" s="4" t="n"/>
+      <c r="E227" s="4" t="n"/>
+      <c r="F227" s="4" t="n"/>
+      <c r="G227" s="4" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="32" t="inlineStr">
+        <is>
+          <t>MQ0301</t>
+        </is>
+      </c>
+      <c r="B228" s="32" t="inlineStr">
+        <is>
+          <t>HERRAMIENTA MENOR</t>
+        </is>
+      </c>
+      <c r="C228" s="32" t="inlineStr">
+        <is>
+          <t>GLB</t>
+        </is>
+      </c>
+      <c r="D228" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E228" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F228" s="34" t="n">
+        <v>1600</v>
+      </c>
+      <c r="G228" s="34" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL EQUIPO:</t>
+        </is>
+      </c>
+      <c r="B229" s="36" t="n"/>
+      <c r="C229" s="36" t="n"/>
+      <c r="D229" s="36" t="n"/>
+      <c r="E229" s="36" t="n"/>
+      <c r="F229" s="36" t="n"/>
+      <c r="G229" s="42" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="32" t="inlineStr">
+        <is>
+          <t>--- MATERIALES ---</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="n"/>
+      <c r="C230" s="4" t="n"/>
+      <c r="D230" s="4" t="n"/>
+      <c r="E230" s="4" t="n"/>
+      <c r="F230" s="4" t="n"/>
+      <c r="G230" s="4" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="32" t="inlineStr">
+        <is>
+          <t>004910</t>
+        </is>
+      </c>
+      <c r="B231" s="32" t="inlineStr">
+        <is>
+          <t>REG.HIE.D=1/2E=1/2 1.5x40M</t>
+        </is>
+      </c>
+      <c r="C231" s="32" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="D231" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E231" s="33" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F231" s="34" t="n">
+        <v>118400</v>
+      </c>
+      <c r="G231" s="34" t="n">
+        <v>118400</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="41" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MATERIALES:</t>
+        </is>
+      </c>
+      <c r="B232" s="36" t="n"/>
+      <c r="C232" s="36" t="n"/>
+      <c r="D232" s="36" t="n"/>
+      <c r="E232" s="36" t="n"/>
+      <c r="F232" s="36" t="n"/>
+      <c r="G232" s="42" t="n">
+        <v>118400</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="43" t="inlineStr">
+        <is>
+          <t>COSTO DIRECTO:</t>
+        </is>
+      </c>
+      <c r="B233" s="44" t="n"/>
+      <c r="C233" s="44" t="n"/>
+      <c r="D233" s="44" t="n"/>
+      <c r="E233" s="44" t="n"/>
+      <c r="F233" s="44" t="n"/>
+      <c r="G233" s="45" t="n">
+        <v>145391</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="46" t="inlineStr">
+        <is>
+          <t>COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B235" s="44" t="n"/>
+      <c r="C235" s="44" t="n"/>
+      <c r="D235" s="44" t="n"/>
+      <c r="E235" s="44" t="n"/>
+      <c r="F235" s="44" t="n"/>
+      <c r="G235" s="44" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="22" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="B236" s="4" t="n"/>
+      <c r="C236" s="4" t="n"/>
+      <c r="D236" s="4" t="n"/>
+      <c r="E236" s="4" t="n"/>
+      <c r="F236" s="23" t="inlineStr">
+        <is>
+          <t>514.34%</t>
+        </is>
+      </c>
+      <c r="G236" s="24" t="n">
+        <v>747799.2610865638</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="22" t="inlineStr">
+        <is>
+          <t>IMPREVISTOS</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="n"/>
+      <c r="C237" s="4" t="n"/>
+      <c r="D237" s="4" t="n"/>
+      <c r="E237" s="4" t="n"/>
+      <c r="F237" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G237" s="24" t="n">
+        <v>7269.55</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="22" t="inlineStr">
+        <is>
+          <t>UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="n"/>
+      <c r="C238" s="4" t="n"/>
+      <c r="D238" s="4" t="n"/>
+      <c r="E238" s="4" t="n"/>
+      <c r="F238" s="23" t="inlineStr">
+        <is>
+          <t>5.00%</t>
+        </is>
+      </c>
+      <c r="G238" s="24" t="n">
+        <v>7269.55</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="22" t="inlineStr">
+        <is>
+          <t>IVA SOBRE LA UTILIDAD</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="n"/>
+      <c r="C239" s="4" t="n"/>
+      <c r="D239" s="4" t="n"/>
+      <c r="E239" s="4" t="n"/>
+      <c r="F239" s="23" t="inlineStr">
+        <is>
+          <t>19.00%</t>
+        </is>
+      </c>
+      <c r="G239" s="24" t="n">
+        <v>27624.29</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL COSTOS INDIRECTOS</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="n"/>
+      <c r="C240" s="4" t="n"/>
+      <c r="D240" s="4" t="n"/>
+      <c r="E240" s="4" t="n"/>
+      <c r="F240" s="23" t="inlineStr">
+        <is>
+          <t>525.29%</t>
+        </is>
+      </c>
+      <c r="G240" s="24" t="n">
+        <v>763719.5755865638</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="43" t="inlineStr">
+        <is>
+          <t>VALOR TOTAL ITEM:</t>
+        </is>
+      </c>
+      <c r="B241" s="44" t="n"/>
+      <c r="C241" s="44" t="n"/>
+      <c r="D241" s="44" t="n"/>
+      <c r="E241" s="44" t="n"/>
+      <c r="F241" s="44" t="n"/>
+      <c r="G241" s="45" t="n">
+        <v>909110.5755865638</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="118">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A205:F205"/>
+    <mergeCell ref="A166:E166"/>
+    <mergeCell ref="A183:F183"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A142:E142"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A216:E216"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A160:F160"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A159:F159"/>
+    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A134:F134"/>
+    <mergeCell ref="A121:F121"/>
+    <mergeCell ref="A139:E139"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A202:F202"/>
+    <mergeCell ref="A137:G137"/>
+    <mergeCell ref="A226:F226"/>
+    <mergeCell ref="A43:E43"/>
+    <mergeCell ref="A165:E165"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A241:F241"/>
+    <mergeCell ref="A93:E93"/>
+    <mergeCell ref="A91:G91"/>
+    <mergeCell ref="A138:E138"/>
+    <mergeCell ref="A119:E119"/>
+    <mergeCell ref="A115:G115"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A118:E118"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A239:E239"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A112:F112"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A232:F232"/>
+    <mergeCell ref="A96:E96"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A153:F153"/>
+    <mergeCell ref="A235:G235"/>
+    <mergeCell ref="A40:E40"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A177:F177"/>
+    <mergeCell ref="A208:F208"/>
+    <mergeCell ref="A217:F217"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A147:G147"/>
+    <mergeCell ref="A237:E237"/>
+    <mergeCell ref="A211:G211"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A187:E187"/>
+    <mergeCell ref="A186:G186"/>
+    <mergeCell ref="A131:F131"/>
+    <mergeCell ref="A66:E66"/>
+    <mergeCell ref="A236:E236"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A189:E189"/>
+    <mergeCell ref="A238:E238"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A213:E213"/>
+    <mergeCell ref="A229:F229"/>
+    <mergeCell ref="A172:G172"/>
+    <mergeCell ref="A143:F143"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A141:E141"/>
+    <mergeCell ref="A196:G196"/>
+    <mergeCell ref="A221:G221"/>
+    <mergeCell ref="A215:E215"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A168:F168"/>
+    <mergeCell ref="A167:E167"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A191:E191"/>
+    <mergeCell ref="A233:F233"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A125:G125"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A192:F192"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A212:E212"/>
+    <mergeCell ref="A106:F106"/>
+    <mergeCell ref="A164:E164"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="A209:F209"/>
+    <mergeCell ref="A184:F184"/>
+    <mergeCell ref="A214:E214"/>
+    <mergeCell ref="A163:E163"/>
+    <mergeCell ref="A162:G162"/>
+    <mergeCell ref="A116:E116"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="A188:E188"/>
+    <mergeCell ref="A140:E140"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A240:E240"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A101:G101"/>
+    <mergeCell ref="A190:E190"/>
+    <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A92:E92"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1200,9 +6342,793 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NOMBRE DE LA EMPRESA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LOGO DE LA EMPRESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="47" t="inlineStr">
+        <is>
+          <t>INSUMOS</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Obra:</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ESCRIBA AQUÍ EL NOMBRE DE LA OBRA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FECHA:</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>19-sept-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>QUIEN ELABORÓ:</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="47" t="inlineStr">
+        <is>
+          <t>MATERIALES</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>CANT.</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>VR. UNIT.</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>VR.TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>GRAVA TRITURADA.3/4</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>52571</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>16559.865</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>"TUBO CONCRETO CII 15""</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>71618</v>
+      </c>
+      <c r="E11" s="34" t="n">
+        <v>71618</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>TUBO CONCRETO CII 1.0M HR</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <v>319129</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>325511.58</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>TABLA 1x10x300 OTOBO</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D13" s="34" t="n">
+        <v>13007</v>
+      </c>
+      <c r="E13" s="34" t="n">
+        <v>32517.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>FORMALETA CAMARA INSPECCIO</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="34" t="n">
+        <v>54213</v>
+      </c>
+      <c r="E14" s="34" t="n">
+        <v>108426</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>HIERR.DE 60000 PSI 420 MPA</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>KLS</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="D15" s="34" t="n">
+        <v>4287</v>
+      </c>
+      <c r="E15" s="34" t="n">
+        <v>293638.065</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>HIERR.DE 37000 PSI 259 MPA</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>KLS</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="34" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E16" s="34" t="n">
+        <v>20600</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>"VAL CHAPAL Q=4.1LT/S D10"</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="34" t="n">
+        <v>2217920</v>
+      </c>
+      <c r="E17" s="34" t="n">
+        <v>2217920</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>"TUBO SAN 12""PVC-315M</t>
+        </is>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="34" t="n">
+        <v>116106</v>
+      </c>
+      <c r="E18" s="34" t="n">
+        <v>116106</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>HIDROSELLO NOVAFORT 315MM</t>
+        </is>
+      </c>
+      <c r="B19" s="33" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="C19" s="34" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D19" s="34" t="n">
+        <v>31766</v>
+      </c>
+      <c r="E19" s="34" t="n">
+        <v>10482.78</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>ADHESIVO NOVAFORT</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>GLN</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="D20" s="34" t="n">
+        <v>86557</v>
+      </c>
+      <c r="E20" s="34" t="n">
+        <v>262.26771</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>ACONDICION SUPERF NOVAFORT</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>GLN</t>
+        </is>
+      </c>
+      <c r="C21" s="34" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="D21" s="34" t="n">
+        <v>100962</v>
+      </c>
+      <c r="E21" s="34" t="n">
+        <v>305.91486</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>MOTOR EL.BOMB 25HP</t>
+        </is>
+      </c>
+      <c r="B22" s="33" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="34" t="n">
+        <v>2779650</v>
+      </c>
+      <c r="E22" s="34" t="n">
+        <v>2779650</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>BOM.SUM. 1 HP</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="34" t="n">
+        <v>2593766</v>
+      </c>
+      <c r="E23" s="34" t="n">
+        <v>2593766</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>REG.HIE.D=1/2E=1/2 1.5x40M</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="34" t="n">
+        <v>118400</v>
+      </c>
+      <c r="E24" s="34" t="n">
+        <v>118400</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="48" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MATERIALES:</t>
+        </is>
+      </c>
+      <c r="B25" s="36" t="n"/>
+      <c r="C25" s="36" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="49" t="n">
+        <v>8705763.972569998</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="47" t="inlineStr">
+        <is>
+          <t>MANO DE OBRA</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN</t>
+        </is>
+      </c>
+      <c r="B28" s="31" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="inlineStr">
+        <is>
+          <t>CANT.</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
+        <is>
+          <t>VR. UNIT.</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="inlineStr">
+        <is>
+          <t>VR.TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA ALBANILERIA1 AYUDANTE</t>
+        </is>
+      </c>
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="C29" s="34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D29" s="34" t="n">
+        <v>8949</v>
+      </c>
+      <c r="E29" s="34" t="n">
+        <v>9306.960000000001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA ALBANILERIA2 AYUDANTE-1 OFI</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="C30" s="34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D30" s="34" t="n">
+        <v>32845</v>
+      </c>
+      <c r="E30" s="34" t="n">
+        <v>410562.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA TOPOGRAFIA1 CADENERO-1 TOP</t>
+        </is>
+      </c>
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="C31" s="34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D31" s="34" t="n">
+        <v>66168</v>
+      </c>
+      <c r="E31" s="34" t="n">
+        <v>661.6800000000001</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA ALBANILERIA 2 AYUDANTE-1 OFI</t>
+        </is>
+      </c>
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="C32" s="34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D32" s="34" t="n">
+        <v>32845</v>
+      </c>
+      <c r="E32" s="34" t="n">
+        <v>36129.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA TOPOGRAFIA 2 CADENERO-1 TOP</t>
+        </is>
+      </c>
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="C33" s="34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D33" s="34" t="n">
+        <v>80691</v>
+      </c>
+      <c r="E33" s="34" t="n">
+        <v>32276.4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA ALBANILERIA2 AYUDANTE</t>
+        </is>
+      </c>
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="C34" s="34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D34" s="34" t="n">
+        <v>17897</v>
+      </c>
+      <c r="E34" s="34" t="n">
+        <v>14317.6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA HIDROSANIT.1 AYUDANTE-1 OFI</t>
+        </is>
+      </c>
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="C35" s="34" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="D35" s="34" t="n">
+        <v>25391</v>
+      </c>
+      <c r="E35" s="34" t="n">
+        <v>226487.72</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t>MANO OBRA ELECTRICAS1 AYUDANTE-1 OFI</t>
+        </is>
+      </c>
+      <c r="B36" s="33" t="inlineStr">
+        <is>
+          <t>HC</t>
+        </is>
+      </c>
+      <c r="C36" s="34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D36" s="34" t="n">
+        <v>33455</v>
+      </c>
+      <c r="E36" s="34" t="n">
+        <v>83637.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="48" t="inlineStr">
+        <is>
+          <t>SUBTOTAL MANO DE OBRA:</t>
+        </is>
+      </c>
+      <c r="B37" s="36" t="n"/>
+      <c r="C37" s="36" t="n"/>
+      <c r="D37" s="36" t="n"/>
+      <c r="E37" s="49" t="n">
+        <v>813379.86</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="47" t="inlineStr">
+        <is>
+          <t>EQUIPO</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>DESCRIPCIÓN</t>
+        </is>
+      </c>
+      <c r="B40" s="31" t="inlineStr">
+        <is>
+          <t>UND</t>
+        </is>
+      </c>
+      <c r="C40" s="31" t="inlineStr">
+        <is>
+          <t>CANT.</t>
+        </is>
+      </c>
+      <c r="D40" s="31" t="inlineStr">
+        <is>
+          <t>VR. UNIT.</t>
+        </is>
+      </c>
+      <c r="E40" s="31" t="inlineStr">
+        <is>
+          <t>VR.TOTAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t>RETROEXCAVADORA CARGADORA</t>
+        </is>
+      </c>
+      <c r="B41" s="33" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="C41" s="34" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D41" s="34" t="n">
+        <v>101150</v>
+      </c>
+      <c r="E41" s="34" t="n">
+        <v>202.3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="32" t="inlineStr">
+        <is>
+          <t>HERRAMIENTA MENOR</t>
+        </is>
+      </c>
+      <c r="B42" s="33" t="inlineStr">
+        <is>
+          <t>GLB</t>
+        </is>
+      </c>
+      <c r="C42" s="34" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="D42" s="34" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E42" s="34" t="n">
+        <v>10624</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="32" t="inlineStr">
+        <is>
+          <t>RETROEXCAVADORA JD-510</t>
+        </is>
+      </c>
+      <c r="B43" s="33" t="inlineStr">
+        <is>
+          <t>HRS</t>
+        </is>
+      </c>
+      <c r="C43" s="34" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D43" s="34" t="n">
+        <v>88000</v>
+      </c>
+      <c r="E43" s="34" t="n">
+        <v>46640</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="48" t="inlineStr">
+        <is>
+          <t>SUBTOTAL EQUIPO:</t>
+        </is>
+      </c>
+      <c r="B44" s="36" t="n"/>
+      <c r="C44" s="36" t="n"/>
+      <c r="D44" s="36" t="n"/>
+      <c r="E44" s="49" t="n">
+        <v>57466.3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="43" t="inlineStr">
+        <is>
+          <t>TOTAL GENERAL:</t>
+        </is>
+      </c>
+      <c r="B47" s="44" t="n"/>
+      <c r="C47" s="44" t="n"/>
+      <c r="D47" s="44" t="n"/>
+      <c r="E47" s="45" t="n">
+        <v>9576610.132569999</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>